--- a/volunteer_registration_forms/036_zimbabwe_nursing_application_form_template--volunteer_registration_forms.xlsx
+++ b/volunteer_registration_forms/036_zimbabwe_nursing_application_form_template--volunteer_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>surname_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Surname</t>
+          <t>Surname 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
+          <t>emergency_contact_relationship_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emergency Contact Relationship</t>
+          <t>Emergency Contact Relationship 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
+          <t>emergency_contact_phone_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Emergency Contact Phone</t>
+          <t>Emergency Contact Phone 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1566,29 +1566,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>university_of_health_sciences</t>
+          <t>university_of_medicine_and_surgery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>University of Health Sciences</t>
+          <t>University of Medicine and Surgery</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>medical_school_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>university_of_medicine_and_surgery</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>University of Medicine and Surgery</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>sibling</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Child</t>
+          <t>Sibling</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sibling</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sibling</t>
+          <t>Partner</t>
         </is>
       </c>
     </row>
@@ -1668,27 +1668,10 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
